--- a/4_analisis/salidas/programas/tablas_programas.xlsx
+++ b/4_analisis/salidas/programas/tablas_programas.xlsx
@@ -455,7 +455,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Los 20 programas de mayor peso en 2026</t>
+          <t>Los 20 programas de mayor peso en 2027</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Importe 2026 (M€)</t>
+          <t>Importe 2027 (M€)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -497,12 +497,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.536,8</t>
+          <t>4.922,5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>38,09</t>
+          <t>39,25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>990,7</t>
+          <t>1.089,6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8,32</t>
+          <t>8,69</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -547,12 +547,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>860,6</t>
+          <t>958,2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>7,64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -567,17 +567,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fondo Canario de Financiación Municipal (942C)</t>
+          <t>Atención a Personas en situación de Dependencia (231M)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>465,3</t>
+          <t>565,5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -592,17 +592,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Transferencias a Cabildos traspaso de competencias (942A)</t>
+          <t>Fondo Canario de Financiación Municipal (942C)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>452,0</t>
+          <t>495,0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3,80</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Atención a Personas en situación de Dependencia (231M)</t>
+          <t>Transferencias a Cabildos traspaso de competencias (942A)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>396,0</t>
+          <t>492,9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -642,12 +642,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Desarrollo Energético (425A)</t>
+          <t>Financiación de las Universidades Canarias (322F)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>285,8</t>
+          <t>301,6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -667,17 +667,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Financiación de las Universidades Canarias (322F)</t>
+          <t>Dirección Administrativa y Servicios Generales (321A)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>281,9</t>
+          <t>257,7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -692,17 +692,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dirección Administrativa y Servicios Generales (321A)</t>
+          <t>Tribunales de Justicia (112A)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>266,2</t>
+          <t>222,2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>214,9</t>
+          <t>215,0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1,80</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -742,22 +742,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tribunales de Justicia (112A)</t>
+          <t>Fondo de desarrollo de Canarias (943A)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>203,3</t>
+          <t>163,4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>1,30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>continua</t>
+          <t>subfuncion</t>
         </is>
       </c>
     </row>
@@ -767,22 +767,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fondo de desarrollo de Canarias (943A)</t>
+          <t>Dirección, Promoción y Gestión en mat. de Vivienda (261A)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>163,4</t>
+          <t>154,0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>subfuncion</t>
+          <t>continua</t>
         </is>
       </c>
     </row>
@@ -792,17 +792,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dirección, Promoción y Gestión en mat. de Vivienda (261A)</t>
+          <t>Amortiz y gtos fros deuda pública moneda nacional (951M)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>162,0</t>
+          <t>150,8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>130,3</t>
+          <t>133,5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -842,17 +842,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amortiz y gtos fros deuda pública moneda nacional (951M)</t>
+          <t>Servicios Complem. a la Enseñanza no Universitaria (324C)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>104,6</t>
+          <t>118,4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Servicios Complem. a la Enseñanza no Universitaria (324C)</t>
+          <t>Movilidad Interior (441D)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>102,2</t>
+          <t>111,5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gestión Patrimonial y contratación pública (923B)</t>
+          <t>Infraestruct. y Serv. de Comunicac. e Informática (491A)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>101,7</t>
+          <t>97,9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Infraestruct. y Serv. de Comunicac. e Informática (491A)</t>
+          <t>Fomento del Empleo (241C)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>99,9</t>
+          <t>91,6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fomento del Empleo (241C)</t>
+          <t>Gestión Patrimonial y contratación pública (923B)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>92,4</t>
+          <t>88,2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,70</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>83,1</t>
+          <t>84,1</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>0,70</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1023,7 +1023,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Programas creados en 2024-2026</t>
+          <t>Programas creados en 2024-2027</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Importe 2026 (M€)</t>
+          <t>Importe 2027 (M€)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>53,3</t>
+          <t>53,4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>4,3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Estudios, form. e investig. en Seguridad Pública (132C)</t>
+          <t>Estudios, formac. e investig. en Seguridad Pública (132C)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1192,7 +1192,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Plan Cofinanciado Mejora de la Red Viaria (453C)</t>
+          <t>Plan Sect. de Infraestr. y Calidad Turíst. de Can. (432C)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1200,19 +1200,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>parcial</t>
+          <t>pendiente</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Atención a personas mayores (231D)</t>
+          <t>Plan Cofinanciado Mejora de la Red Viaria (453C)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16,2</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1230,27 +1230,47 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Plan Sect. de Infraestr. y Calidad Turíst. de Can. (432C)</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Atención a personas mayores (231D)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>2026</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>18,1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>parcial</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Plan Sect. de Infraestructuras y Calidad Turística (432C)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Nota. Alta = primer año con el programa en la serie oficial.</t>
         </is>
@@ -1314,7 +1334,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2027</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1354,7 @@
         <v>3.49</v>
       </c>
       <c r="E5" t="n">
-        <v>3.91</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="6">
@@ -1353,7 +1373,7 @@
         <v>0.25</v>
       </c>
       <c r="E6" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="7">
@@ -1372,7 +1392,7 @@
         <v>0.84</v>
       </c>
       <c r="E7" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1410,7 +1430,7 @@
         <v>23.45</v>
       </c>
       <c r="E9" t="n">
-        <v>21.91</v>
+        <v>22.71</v>
       </c>
     </row>
     <row r="10">
@@ -1429,7 +1449,7 @@
         <v>1.17</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="11">
@@ -1448,7 +1468,7 @@
         <v>0.89</v>
       </c>
       <c r="E11" t="n">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="12">
@@ -1486,7 +1506,7 @@
         <v>36.86</v>
       </c>
       <c r="E13" t="n">
-        <v>38.14</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="14">
@@ -1505,7 +1525,7 @@
         <v>28.7</v>
       </c>
       <c r="E14" t="n">
-        <v>29.52</v>
+        <v>27.28</v>
       </c>
     </row>
     <row r="15">
@@ -1524,7 +1544,7 @@
         <v>1.47</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="16">
@@ -1543,7 +1563,7 @@
         <v>1.25</v>
       </c>
       <c r="E16" t="n">
-        <v>1.23</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17">
@@ -1562,7 +1582,7 @@
         <v>1.45</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="19">
@@ -1612,7 +1632,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>% del importe 2026</t>
+          <t>% del importe 2027</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1644,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>96,9</t>
+          <t>97,2</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,5</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1680,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,5</t>
         </is>
       </c>
     </row>
